--- a/output/HS_Code_Summary_Hitachi_Energy_139788.xlsx
+++ b/output/HS_Code_Summary_Hitachi_Energy_139788.xlsx
@@ -790,10 +790,12 @@
       </c>
       <c r="D17" s="9">
         <f>$B$13*F17/$F$23</f>
+        <v>2.1299980041248086</v>
         <v/>
       </c>
       <c r="E17" s="9">
         <f>$B$14*F17/$F$23</f>
+        <v>3.148692701749717</v>
         <v/>
       </c>
       <c r="F17" s="10" t="n">
@@ -826,10 +828,12 @@
       </c>
       <c r="D18" s="9">
         <f>$B$13*F18/$F$23</f>
+        <v>9.364646397445279</v>
         <v/>
       </c>
       <c r="E18" s="9">
         <f>$B$14*F18/$F$23</f>
+        <v>13.84339032665824</v>
         <v/>
       </c>
       <c r="F18" s="10" t="n">
@@ -862,10 +866,12 @@
       </c>
       <c r="D19" s="9">
         <f>$B$13*F19/$F$23</f>
+        <v>2.7726698157141905</v>
         <v/>
       </c>
       <c r="E19" s="9">
         <f>$B$14*F19/$F$23</f>
+        <v>4.09872929279489</v>
         <v/>
       </c>
       <c r="F19" s="10" t="n">
@@ -898,10 +904,12 @@
       </c>
       <c r="D20" s="9">
         <f>$B$13*F20/$F$23</f>
+        <v>4.988357394717584</v>
         <v/>
       </c>
       <c r="E20" s="9">
         <f>$B$14*F20/$F$23</f>
+        <v>7.374093540017298</v>
         <v/>
       </c>
       <c r="F20" s="10" t="n">
@@ -934,10 +942,12 @@
       </c>
       <c r="D21" s="9">
         <f>$B$13*F21/$F$23</f>
+        <v>2.455924422859424</v>
         <v/>
       </c>
       <c r="E21" s="9">
         <f>$B$14*F21/$F$23</f>
+        <v>3.6304969729226264</v>
         <v/>
       </c>
       <c r="F21" s="10" t="n">
@@ -970,10 +980,12 @@
       </c>
       <c r="D22" s="9">
         <f>$B$13*F22/$F$23</f>
+        <v>1.2884039651387134</v>
         <v/>
       </c>
       <c r="E22" s="9">
         <f>$B$14*F22/$F$23</f>
+        <v>1.9045971658572285</v>
         <v/>
       </c>
       <c r="F22" s="10" t="n">
@@ -1003,18 +1015,22 @@
       </c>
       <c r="C23" s="13">
         <f>SUM(C17:C22)</f>
+        <v>16.0</v>
         <v/>
       </c>
       <c r="D23" s="14">
         <f>SUM(D17:D22)</f>
+        <v>23.0</v>
         <v/>
       </c>
       <c r="E23" s="14">
         <f>SUM(E17:E22)</f>
+        <v>34.0</v>
         <v/>
       </c>
       <c r="F23" s="15">
         <f>SUM(F17:F22)</f>
+        <v>15031.0</v>
         <v/>
       </c>
       <c r="G23" s="16" t="n"/>
@@ -1398,12 +1414,14 @@
       <c r="C11" s="16" t="n"/>
       <c r="D11" s="24">
         <f>SUM(D4:D10)</f>
+        <v>16.0</v>
         <v/>
       </c>
       <c r="E11" s="16" t="n"/>
       <c r="F11" s="16" t="n"/>
       <c r="G11" s="25">
         <f>SUM(G4:G10)</f>
+        <v>15031.0</v>
         <v/>
       </c>
     </row>
